--- a/education_forms/037_final_study_guide_quiz--education_forms.xlsx
+++ b/education_forms/037_final_study_guide_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>study_guide_1</t>
+          <t>section_1_review</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -561,20 +561,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>answer_1</t>
+          <t>section_2_questions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Answer 1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Section 2 - Questions</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide 2-5 questions with correct answers</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,17 +588,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>confidence_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Confidence level</t>
+          <t>What is the correct answer to this question?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +611,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback_1</t>
+          <t>section_2_answers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Student feedback</t>
+          <t>Section 2 - Answers</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,19 +639,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>section_2_1</t>
+          <t>section_3_review</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Section 2 - Questions</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Please provide 2-5 questions with correct answers</t>
-        </is>
-      </c>
+          <t>Section 3 - Review</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -657,17 +657,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>confidence_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is the main topic of this unit?</t>
+          <t>Confidence level</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,20 +680,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>section_4_questions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Another question</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Section 4 - Questions</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide 2-5 questions with correct answers</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -708,12 +712,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>More questions</t>
+          <t>Question 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -731,12 +735,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>section_2_2</t>
+          <t>section_4_answers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Section 2 - Answers</t>
+          <t>Section 4 - Answers</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -754,12 +758,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>confidence_2</t>
+          <t>section_5_review</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Confidence level</t>
+          <t>Section 5 - Review</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,17 +776,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>feedback_2</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Student feedback</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -795,24 +799,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>section_3_1</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Section 3 - Review</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Please provide 2-5 questions with correct answers</t>
-        </is>
-      </c>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -827,12 +827,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Another question</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -845,278 +845,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>final_feedback</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>More questions</t>
+          <t>Final Feedback</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>section_3_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Section 3 - Answers</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>confidence_3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Confidence level</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>feedback_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Student feedback</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>section_4_1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Section 4 - Questions</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Please provide 2-5 questions with correct answers</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>question_7</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Another question</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>question_8</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>More questions</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>section_4_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Section 4 - Answers</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>confidence_4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Confidence level</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>feedback_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Student feedback</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1133,10 +876,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1212,102 +955,102 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>answer_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>answer_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Answer 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>answer_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Answer 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>answer_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>answer_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Answer 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>section_2_answers_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>topic_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Topic 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>section_2_answers_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>topic_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Topic 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>section_2_answers_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>topic_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Topic 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1062,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>answer_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Answer 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1336,12 +1079,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Answer 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1353,503 +1096,146 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>answer_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Answer 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>section_4_answers_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>answer_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Answer 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>section_4_answers_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>answer_5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Answer 5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>section_4_answers_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>answer_6</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Answer 6</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>section_2_2_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>answer_1</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Answer 1</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>section_2_2_choices</t>
+          <t>submit_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Answer 2</t>
+          <t>Exit</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>section_2_2_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>answer_3</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Answer 3</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>answer_1</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Answer 1</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>Answer 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>question_5_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>answer_3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Answer 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>answer_4</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Answer 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>answer_5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Answer 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>question_6_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>answer_6</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Answer 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>section_3_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>answer_1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Answer 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>section_3_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>answer_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Answer 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>section_3_2_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>answer_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Answer 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>answer_1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Answer 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>answer_2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Answer 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>question_7_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>answer_3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Answer 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>answer_4</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Answer 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>answer_5</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Answer 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>question_8_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>answer_6</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Answer 6</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>section_4_2_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>answer_1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Answer 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>section_4_2_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>answer_2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Answer 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>section_4_2_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>answer_3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Answer 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>submit_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>submit_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>exit</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>category_1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Category 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>category_2</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Category 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>category_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>category_3</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
         <is>
           <t>Category 3</t>
         </is>
